--- a/survey_templates/045_cost_efficiency_progress_survey--survey_templates.xlsx
+++ b/survey_templates/045_cost_efficiency_progress_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cost Efficiency Progress</t>
+          <t>Project Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,20 +548,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Project Status</t>
+          <t>Project Start Date</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,24 +571,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cost Efficiency Score</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Score from 1-5</t>
-        </is>
-      </c>
+          <t>Project End Date</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -598,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Time Period</t>
+          <t>Project Duration</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -621,20 +617,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Project Type</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -644,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Efficiency</t>
+          <t>Project Status</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -667,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Cost Efficiency Score</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -690,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Time Period</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -713,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Cost Center</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,20 +732,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Project Name</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Efficiency</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -782,13 +778,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -805,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Project Status</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -818,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -828,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cost Center</t>
+          <t>Project Team</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -851,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Project Type</t>
+          <t>Project Location</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -864,7 +860,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -874,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Time Period</t>
+          <t>Page 16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -887,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -897,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Project Start</t>
+          <t>Page 17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -927,167 +923,6 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Project Duration</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Project Location</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Project Team</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Project Status</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Cost Center</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Project Type</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1102,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1130,34 +965,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1186,46 +1021,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1254,352 +1089,114 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>page_13_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>page_13_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>page_14_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>page_14_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>page_15_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>page_15_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>page_15_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>page_15_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>page_20_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>page_20_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>page_22_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>page_22_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>page_23_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>page_23_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>page_24_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>page_24_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>page_25_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>page_25_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
